--- a/ig/DM-37/ValueSet-JDV-ModeleDocumentCDANonStructure.xlsx
+++ b/ig/DM-37/ValueSet-JDV-ModeleDocumentCDANonStructure.xlsx
@@ -8,13 +8,12 @@
   <sheets>
     <sheet name="Metadata" r:id="rId3" sheetId="1"/>
     <sheet name="Include from TRE_R221_ModeleD" r:id="rId4" sheetId="2"/>
-    <sheet name="Exclude from TRE_R221_ModeleD" r:id="rId5" sheetId="3"/>
   </sheets>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="44" uniqueCount="37">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="34" uniqueCount="33">
   <si>
     <t>Property</t>
   </si>
@@ -113,18 +112,6 @@
   </si>
   <si>
     <t>https://mos.esante.gouv.fr/NOS/TRE_R221-ModeleDocumentCDANonStructure/FHIR/TRE-R221-ModeleDocumentCDANonStructure</t>
-  </si>
-  <si>
-    <t>Operation</t>
-  </si>
-  <si>
-    <t>concept</t>
-  </si>
-  <si>
-    <t>is-not-a</t>
-  </si>
-  <si>
-    <t>dateFin</t>
   </si>
 </sst>
 </file>
@@ -424,56 +411,4 @@
   </sheetData>
   <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15.0"/>
-  <cols>
-    <col min="1" max="1" width="30.703125" customWidth="true"/>
-    <col min="2" max="2" width="50.703125" customWidth="true"/>
-  </cols>
-  <sheetData>
-    <row r="1">
-      <c r="A1" t="s" s="1">
-        <v>0</v>
-      </c>
-      <c r="B1" t="s" s="1">
-        <v>33</v>
-      </c>
-      <c r="C1" t="s" s="1">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="s" s="2">
-        <v>34</v>
-      </c>
-      <c r="B2" t="s" s="2">
-        <v>35</v>
-      </c>
-      <c r="C2" t="s" s="2">
-        <v>36</v>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="s" s="2">
-        <v>30</v>
-      </c>
-      <c r="B3" t="s" s="2">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="s" s="2">
-        <v>31</v>
-      </c>
-      <c r="B4" t="s" s="2">
-        <v>32</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins bottom="0.75" footer="0.3" header="0.3" left="0.7" right="0.7" top="0.75"/>
-</worksheet>
 </file>